--- a/光伏配储项目/电价数据/2026/国安站.xlsx
+++ b/光伏配储项目/电价数据/2026/国安站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55425</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.61517</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.9815700000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.16959</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.11094</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.05046</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.88827</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.89428</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.60965</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.6626599999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.5952499999999999</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.87025</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.87027</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.8642300000000001</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.58853</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.8753500000000001</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.85201</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.86811</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.87712</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.6175</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.8759</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.8823</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.63691</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.90715</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.99512</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.88849</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.69611</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6904600000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.47127</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.75859</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7818099999999999</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.0509</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.0402</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.13189</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.76067</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.72366</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50886</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.79328</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.98726</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34978</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7858200000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.7940900000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.96287</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.92671</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.07807</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.35468</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.21057</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.24989</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7493200000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.25619</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.19768</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10654</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.25699</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.55074</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.18803</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.28488</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.50099</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.34181</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.26051</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.38143</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.31367</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8184</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.1931</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04641</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18304</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51635</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.6852</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.58745</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.65952</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.5575800000000001</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.62551</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.59296</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.5994700000000001</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.5930299999999999</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.59009</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.64402</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.88973</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.21666</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.9109299999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.66349</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5571</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.6160099999999999</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.52786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.5611499999999999</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.96277</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.17564</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.8009500000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13174</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.06105</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.02369</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.72784</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.55596</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.57888</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.69936</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.20146</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.26678</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.51685</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.19684</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.67087</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09303</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.84656</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.27978</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.17073</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29746</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6263</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.65311</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57625</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62747</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.21217</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.20393</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.21153</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.20466</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18358</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19869</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.1954</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.6761</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.1992</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20799</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.26586</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.5639</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.48014</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.20437</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50638</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26645</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.75666</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7638200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91408</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.65718</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.78213</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.76998</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5771799999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.64136</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.11262</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.72492</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.7165900000000001</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.6784199999999999</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.63432</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.74921</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.58135</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.71711</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.5469299999999999</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.5697000000000001</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.62718</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.5878099999999999</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.5891900000000001</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.59535</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.70829</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.12054</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.88206</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7678700000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71458</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60964</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64142</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.74622</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.1851</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.56248</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.69748</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19398</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.67325</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19606</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.20045</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.8095800000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.97563</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.20237</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.20241</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.90883</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56341</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47723</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.68004</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18952</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.05418</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.20083</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.44202</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.28425</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.1998</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22368</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.2146</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.44983</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.29367</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.30863</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.67067</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.21774</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.21557</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.07178</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.10411</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.12498</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.11105</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.24049</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.19617</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.28378</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.02488</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.77054</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.72793</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53891</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.16042</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.80731</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7905800000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.64178</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.7624099999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.93168</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.61364</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.78212</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.70566</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.6140399999999999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.77138</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.71882</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.65684</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.60215</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.59788</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.5268200000000001</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.46106</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.60385</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.6049500000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.69462</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.5876</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.56687</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.52913</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.51458</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.68763</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72466</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9424600000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.19705</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.34044</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.86375</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.58278</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67264</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.91342</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.89549</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.19065</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44762</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.7794</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9887400000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.2495</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.7102200000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.1181</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.49292</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6705399999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.02678</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.12815</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.26652</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.20033</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.10153</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.01665</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03547</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99942</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.29763</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.47843</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.81501</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.38376</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.23538</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.86656</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10764</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18745</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13465</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.19046</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28702</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34734</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.19029</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.30085</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20451</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19203</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.1861</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21732</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22956</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.21525</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.1923</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.19027</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7434700000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5319199999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.74764</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.322</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.75021</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49986</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48485</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.5113799999999999</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.53073</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46293</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.72881</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.86225</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.62551</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.71376</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7392000000000001</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8598</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71733</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5603899999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55943</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54801</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.6027100000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47904</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10248</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55635</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.52375</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.65034</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51264</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49218</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40328</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49262</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.60898</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.51362</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51255</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49162</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34431</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.21984</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9975700000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.01267</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.7065399999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.63939</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.6033999999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.63849</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.6192799999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.61782</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.8695499999999999</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.62781</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.6167999999999999</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.6172799999999999</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.6176</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07496999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08408</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13126</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04647</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00361</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04626</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04504</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43045</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.67384</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.63735</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.65207</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.63824</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.6377999999999999</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33458</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.63553</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.5482400000000001</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.9023600000000001</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.6944400000000001</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6685099999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.68608</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7687999999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9674299999999999</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.74694</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7499</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.91396</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.66665</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5483300000000001</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48523</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45703</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09437999999999999</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74558</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.75107</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6552100000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6145900000000001</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7403099999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7912899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6110800000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.75474</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03121</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.4321</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.86172</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.46175</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.3491</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.81289</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40716</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.06572</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42752</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.78871</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46602</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7875700000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8010499999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7855599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87915</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5026</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41217</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21927</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5414099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.6880299999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.64975</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.65932</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.57939</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.66031</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.64767</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.5496599999999999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.63615</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.6191599999999999</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.6197999999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.6175499999999999</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.6182799999999999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.64078</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.61895</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.63771</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.54277</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.72509</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.54969</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60021</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56484</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66701</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07796</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.64774</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50925</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57716</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59675</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00978</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34258</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.31119</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27303</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.56121</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8002100000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57662</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65662</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5586599999999999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.99033</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7876799999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.73637</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.65162</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5837899999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.02271</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.03123</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.7124199999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.65003</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.7263099999999999</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.66003</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.7054400000000001</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.79006</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.68956</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.7043700000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.61078</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.59245</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.70397</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.73098</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.6938200000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.72676</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.73826</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.78537</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.73223</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.78874</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.73811</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.73883</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.7380399999999999</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.7261599999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.71913</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6983200000000001</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.71904</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.6797799999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.63897</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.68368</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.64464</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.6600199999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.64555</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.63647</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.63007</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.54013</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.63918</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.7339</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.72472</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.62552</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.6347</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.57399</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.60773</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.54967</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.66499</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.53366</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6304</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.75109</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.90126</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15464</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.94192</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.56111</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12617</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.86886</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.97737</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.88635</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65462</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.83623</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.09823</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.64625</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.5344800000000001</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.9050199999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.09303</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.74705</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.23763</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8085599999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.83978</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.82611</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.76125</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47814</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50062</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20069</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51814</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.8038099999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.77085</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.19153</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.93531</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.65844</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.76253</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7157899999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.57916</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.17792</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.6361</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.92315</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.60053</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.6706</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.42109</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.34447</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.31248</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.60196</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.09383</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.54275</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6169</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8729199999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52969</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.76458</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.09735</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09618</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9362699999999999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.9967</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9505800000000001</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18725</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18604</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8896000000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18604</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63185</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99837</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.04227</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18607</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.97881</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.01975</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.60886</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.95125</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00814</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.11536</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.91264</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.90027</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12524</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.61467</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9870599999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.0246</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.75897</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33601</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.71396</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.58475</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.5868099999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.5783200000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.5014700000000001</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.61574</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.72453</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.59374</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.56348</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.58909</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.56674</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.61217</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83586</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7202499999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.67875</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.64424</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.96641</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.15877</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.64632</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.6484800000000001</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.65023</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.58614</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.58723</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.64018</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.72646</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.6920299999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.64628</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.52798</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.52154</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.5313099999999999</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.53359</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6886599999999999</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.59941</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.57929</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.58038</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.57841</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5841000000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.69104</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.6273300000000001</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.62337</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.64715</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.56767</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.5986399999999999</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.49857</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.43593</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.62739</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.6274500000000001</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.6134700000000001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.56343</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.55538</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.5270499999999999</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5588500000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48722</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7056399999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60598</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62654</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84697</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26778</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16313</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8502000000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70012</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.93798</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16485</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11881</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01552</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5411699999999999</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49692</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56596</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.5345800000000001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.5317000000000001</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.53459</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.5026499999999999</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.60822</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.50186</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.43946</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.50378</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.5580499999999999</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.58113</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.65434</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.95792</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.30045</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.19667</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00172</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9904400000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.99202</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56119</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55241</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9437300000000001</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08348</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79208</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.0105</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77609</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65664</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64938</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71668</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79675</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.2944</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7609400000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.34874</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.48535</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.15755</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.9849199999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.65045</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63208</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66571</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67908</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67415</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.65113</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67562</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20674</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70856</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.79034</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70585</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71362</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72178</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.64065</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75607</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01891</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12828</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69968</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70812</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.7019</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78152</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73168</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8208200000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6720499999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46511</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.16003</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.5394800000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.65455</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.5299299999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.56337</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34489</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.52436</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.67474</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.26097</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.5501900000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.6068600000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.5640499999999999</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.5367000000000001</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.6265299999999999</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.60746</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.53898</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.51564</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75407</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49544</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28472</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.93023</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48352</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18997</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90012</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7615299999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45728</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5000599999999999</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.49177</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.51354</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75366</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51822</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70303</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49869</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42857</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66965</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.59614</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.55628</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.92589</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.5445800000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.49439</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.44155</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.42157</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51571</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41827</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.75973</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76622</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39382</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.5439700000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50085</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7198</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76042</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55288</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50097</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01783</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48197</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44263</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09106</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12676</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.07983</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.1106</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12725</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.0172</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19294</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14121</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13014</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17573</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.8418600000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19048</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84803</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.33999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90119</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.70654</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.7557999999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9468099999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.47929</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.6153099999999999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.60426</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.63981</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.5244099999999999</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7603099999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.41486</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.52755</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.59028</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.74785</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.7400099999999999</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.6030800000000001</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.58539</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.6938500000000001</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.70962</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.71284</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.59794</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.7180599999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.6059</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.69963</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.5628099999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.50878</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.51486</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.5148200000000001</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.5624199999999999</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.53108</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.68884</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.53126</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.7623799999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.11436</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7625700000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.30075</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.36119</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.7439</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66584</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36975</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00539</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.61186</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.50112</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.54915</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.60077</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.7523300000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.2022</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.70657</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.93989</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.68147</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9616699999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.9058099999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76483</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73454</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18605</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18724</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.45141</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26521</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.66706</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.25054</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29409</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.11441</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.43768</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.0419</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.79072</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.74663</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.23641</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.66464</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48319</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.53561</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48796</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.53232</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5349299999999999</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79896</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.68487</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.66735</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50355</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08642</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69277</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66543</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.80275</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.08322</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19561</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.5002099999999999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19894</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54676</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15937</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5574600000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57076</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50214</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23504</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46311</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51096</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46034</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43337</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.54343</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.60738</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7613300000000001</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.1398</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.63875</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46336</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59105</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48426</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46396</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46504</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55448</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46147</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.5754900000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.55049</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.5551900000000001</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.57362</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.53486</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.38173</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.94129</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.45328</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.51644</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.50502</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23468</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15642</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.73978</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21768</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.14332</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.70033</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.56864</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.60358</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80912</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46827</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49108</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10391</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38704</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.99172</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5263600000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.76154</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.76135</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.5157200000000001</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55996</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42777</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44524</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.58568</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.9639800000000001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6515700000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80476</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45551</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.76101</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52998</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.3692</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.37255</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24572</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.09007</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.98882</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.3191</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5522999999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49838</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5843200000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.76176</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5512699999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5500900000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.23796</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7654299999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.76264</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.58558</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45314</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49887</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01526</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7732599999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.62897</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.76179</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.20676</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.75264</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.64048</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.27011</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.90334</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.8876000000000001</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.90803</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17825</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6518699999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.96149</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6957000000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9874700000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.66179</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.68065</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.7616</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.66227</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26582</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04568</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02772</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.0367</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.55094</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36655</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.05949</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.76071</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34555</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.56001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80814</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.55306</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75748</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7593099999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56265</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47102</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.46051</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.63924</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59634</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.56455</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5434099999999999</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45302</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48233</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50058</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.56074</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81388</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17913</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.1344</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.04729</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.13713</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.75153</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74627</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.05813</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.07649</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.6849299999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5545399999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5609700000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.56186</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.48022</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48568</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.55022</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5473</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.66249</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55714</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05302</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.66371</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.55041</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.5002799999999999</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48315</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.50034</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.50056</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57874</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5583400000000001</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.56209</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49861</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5145299999999999</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.56211</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66226</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17717</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.08068</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.66286</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5841499999999999</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.16645</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.87193</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.66242</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.16514</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83969</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51236</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49974</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53572</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34455</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.8510800000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.65591</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6636599999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.9138200000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.63701</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40563</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.63039</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.59039</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42135</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6434</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03324</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.21908</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9347799999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9884400000000001</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03587</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.97919</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.94663</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97727</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.96008</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9448099999999999</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9472999999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.75252</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.12737</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.71426</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.1233</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.20773</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.18959</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.73015</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9501799999999999</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.87025</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.93721</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.55002</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.69264</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.71511</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.76346</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.21206</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.09231</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.03203</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.34369</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.02748</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.1264</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.9313899999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7652</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.7643799999999999</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8239099999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70756</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69047</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5650499999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69287</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7420099999999999</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.70096</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.76144</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7111499999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46587</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7506799999999999</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5245299999999999</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.51106</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02623</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.92395</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03619</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93441</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.04402</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02685</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02703</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.26511</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09702</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.19096</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5485800000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68187</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.62593</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7380800000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7230599999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02293</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72365</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77667</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.15002</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.31773</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.53235</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.69184</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.29943</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.46429</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.07297</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.50138</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.48061</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.75503</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.52251</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.52433</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81326</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.76927</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80875</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.65411</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.76059</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8089700000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.30963</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.0013</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.93141</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9576399999999999</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03631</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16408</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.07074</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86165</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6921799999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.2387</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21402</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21531</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14751</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70084</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.0925</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10408</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10414</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13285</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10178</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51928</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.19718</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.65827</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.58499</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.1527</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.74922</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.68016</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18148</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.87383</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.05863</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.05302</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.07857</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03868</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06646</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12481</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04793</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05854</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18253</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16139</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.20147</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.2014</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29943</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16738</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.15875</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11734</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09796</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12404</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17367</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19109</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17167</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.11341</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.69047</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.62724</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57575</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37557</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.54625</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31001</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.30751</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06509</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48139</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5192599999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.47052</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.47582</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.47232</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.46989</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.46504</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.46895</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.4619</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.44974</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.43965</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.57721</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.70109</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.71668</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.66799</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9567599999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7684800000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.96213</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17403</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.32786</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.47216</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.45921</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45614</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.57041</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.26788</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8504299999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.60256</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7366200000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50147</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84372</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8831100000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.2459</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.7755299999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57924</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58525</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.64425</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.72711</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.6057100000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7521100000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.62697</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.2161</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.19043</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41811</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.19243</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.18856</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.19571</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.12742</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.10167</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20681</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.12862</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.21473</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.07564</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.10507</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.2058</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.11042</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.55294</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.81037</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80371</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56386</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.23193</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.8487</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8492000000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5544</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5629700000000001</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51534</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55375</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49491</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5473600000000001</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.51979</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5201</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55703</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17476</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8823799999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49268</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.20239</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.5081</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5699500000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84458</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7955800000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59717</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85185</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52122</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5456299999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17597</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70043</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5545099999999999</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.18208</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5484600000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5491200000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58025</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79898</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5540499999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7970499999999999</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8484299999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17326</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79799</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68308</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17478</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17971</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.18361</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.18142</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82202</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73533</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.65442</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6851799999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.69372</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73353</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83305</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81645</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.62178</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.81562</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7646499999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.14397</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.76676</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6089199999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.6508200000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64632</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.62041</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61621</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.72004</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6787000000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.82825</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.7038099999999999</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60797</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5123799999999999</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
